--- a/data/trans_bre/P1418-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1418-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 7,3</t>
+          <t>0,29; 7,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,44</t>
+          <t>-0,27; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,9</t>
+          <t>-0,27; 5,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,8</t>
+          <t>0,2; 4,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 232,61</t>
+          <t>1,72; 244,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 984,39</t>
+          <t>-40,39; 1165,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 518,48</t>
+          <t>-22,33; 564,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 253,9</t>
+          <t>-2,72; 237,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>133,78%</t>
+          <t>131,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,27</t>
+          <t>-2,03; 4,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,31</t>
+          <t>0,45; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,53</t>
+          <t>-0,07; 3,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,9</t>
+          <t>0,97; 5,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 132,36</t>
+          <t>-32,73; 128,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 835,89</t>
+          <t>-16,82; 703,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,76; —</t>
+          <t>-39,23; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 353,93</t>
+          <t>25,4; 342,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,51</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>347,78%</t>
+          <t>211,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,53</t>
+          <t>0,13; 10,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,31</t>
+          <t>3,83; 13,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 12,4</t>
+          <t>2,15; 11,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 18,24</t>
+          <t>6,05; 15,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 247,32</t>
+          <t>-2,19; 225,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,83; 564,46</t>
+          <t>87,76; 506,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,85; 1104,56</t>
+          <t>53,61; 911,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138,95; 1452,21</t>
+          <t>93,36; 405,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,47%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,81</t>
+          <t>-0,94; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,55</t>
+          <t>-0,35; 4,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,84</t>
+          <t>0,13; 3,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,78</t>
+          <t>-1,07; 2,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 65,29</t>
+          <t>-12,75; 68,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 119,86</t>
+          <t>-7,95; 107,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 182,44</t>
+          <t>3,49; 181,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,87; 34,22</t>
+          <t>-14,63; 52,97</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>149,78%</t>
+          <t>199,07%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 8,26</t>
+          <t>0,4; 7,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,68</t>
+          <t>6,72; 12,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,59</t>
+          <t>2,11; 7,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,01</t>
+          <t>6,66; 11,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 161,17</t>
+          <t>3,96; 158,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>138,96; 568,9</t>
+          <t>123,01; 510,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,46; 203,38</t>
+          <t>34,77; 204,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>65,52; 281,81</t>
+          <t>113,1; 342,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>341,4%</t>
+          <t>378,45%</t>
         </is>
       </c>
     </row>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 13,88</t>
+          <t>9,6; 13,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,72</t>
+          <t>9,29; 14,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,14</t>
+          <t>7,85; 11,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,14</t>
+          <t>1,12; 9,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>375,65; 4974,39</t>
+          <t>387,03; 4820,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>326,28; 3679,84</t>
+          <t>329,58; 3994,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 4157,96</t>
+          <t>-3,64; 3944,59</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>106,5%</t>
+          <t>108,98%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,9</t>
+          <t>3,43; 6,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,81</t>
+          <t>5,45; 7,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,93</t>
+          <t>3,67; 5,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,6</t>
+          <t>3,64; 5,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,56; 119,61</t>
+          <t>54,99; 123,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>151,43; 287,51</t>
+          <t>154,24; 297,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>131,62; 290,69</t>
+          <t>128,56; 280,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,36; 169,02</t>
+          <t>75,8; 150,35</t>
         </is>
       </c>
     </row>
